--- a/data/trans_orig/Q5416-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5416-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse por su casa en 2007</t>
+          <t>Población según si es capaz de moverse por su casa en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2343</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1837</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7868</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,26%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2343</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>8061</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8240</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2343</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7017</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>10945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>13782</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19342</t>
+          <t>19697</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -959,97 +959,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1837</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1887</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>1873</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103916</t>
+          <t>104044</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113109</t>
+          <t>112366</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134233</t>
+          <t>132939</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146052</t>
+          <t>145412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>241774</t>
+          <t>240973</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>256689</t>
+          <t>256422</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5300</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7857</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>14699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4337</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17109</t>
+          <t>17408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9036</t>
+          <t>7182</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135660</t>
+          <t>135042</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144846</t>
+          <t>144855</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>162682</t>
+          <t>162828</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>177041</t>
+          <t>177017</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>304041</t>
+          <t>303658</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>320229</t>
+          <t>319887</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>891</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>7819</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>884</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11535</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13629</t>
+          <t>13894</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -2097,97 +2097,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1125</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1942</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5603</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1125</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5634</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5312</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1125</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>6205</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97624</t>
+          <t>97763</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119924</t>
+          <t>120214</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131702</t>
+          <t>131748</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>221834</t>
+          <t>221048</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>234961</t>
+          <t>234623</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,67%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>900</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>1689</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10993</t>
+          <t>10239</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>804</t>
+          <t>812</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>8841</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8798</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>131192</t>
+          <t>130524</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>137217</t>
+          <t>136407</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>192830</t>
+          <t>193563</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204625</t>
+          <t>204704</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>327140</t>
+          <t>327115</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>340267</t>
+          <t>340244</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>823</t>
+          <t>830</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7652</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>17001</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>20493</t>
+          <t>21080</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5626</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18399</t>
+          <t>18310</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13094</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32095</t>
+          <t>32747</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21128</t>
+          <t>21768</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44083</t>
+          <t>43671</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2221</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13380</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14438</t>
+          <t>14575</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>478730</t>
+          <t>480822</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>493920</t>
+          <t>494332</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>626662</t>
+          <t>625528</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>651232</t>
+          <t>649966</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1113874</t>
+          <t>1112749</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1141281</t>
+          <t>1140217</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse por su casa en 2012</t>
+          <t>Población según si es capaz de moverse por su casa en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7318</t>
+          <t>7310</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10766</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13021</t>
+          <t>13593</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17067</t>
+          <t>16129</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6256</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>19697</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -4036,97 +4036,97 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>2049</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>129776</t>
+          <t>129601</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138484</t>
+          <t>138475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145017</t>
+          <t>145303</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>159398</t>
+          <t>159242</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>278606</t>
+          <t>278723</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>295724</t>
+          <t>295005</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,3%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>11740</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4310</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16659</t>
+          <t>16180</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7809</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23119</t>
+          <t>21875</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10089</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5721</t>
+          <t>5558</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19429</t>
+          <t>18943</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25327</t>
+          <t>24463</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135975</t>
+          <t>134610</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>149415</t>
+          <t>149286</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>160729</t>
+          <t>161701</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>178192</t>
+          <t>179028</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>301106</t>
+          <t>301886</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>324058</t>
+          <t>323608</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2967</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>15804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17570</t>
+          <t>17363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11766</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>14525</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11969</t>
+          <t>12277</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89659</t>
+          <t>89764</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>102454</t>
+          <t>101580</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117535</t>
+          <t>116664</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133641</t>
+          <t>133341</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>214983</t>
+          <t>213072</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>233826</t>
+          <t>232583</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13192</t>
+          <t>12644</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3072</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14294</t>
+          <t>14208</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8556</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16825</t>
+          <t>16473</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20358</t>
+          <t>19900</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>981</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>150623</t>
+          <t>149949</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159686</t>
+          <t>159708</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>216114</t>
+          <t>215995</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>373366</t>
+          <t>372907</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>390771</t>
+          <t>391043</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17012</t>
+          <t>16695</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>18219</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>38533</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>26296</t>
+          <t>26417</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50931</t>
+          <t>50890</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6380</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>19239</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25049</t>
+          <t>24640</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48830</t>
+          <t>49031</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34674</t>
+          <t>34310</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61633</t>
+          <t>62494</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>972</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12508</t>
+          <t>13003</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10961</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>19217</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>522543</t>
+          <t>523398</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>542765</t>
+          <t>543478</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>658704</t>
+          <t>658809</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>690112</t>
+          <t>690999</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1190018</t>
+          <t>1189535</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1227825</t>
+          <t>1227225</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,21%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse por su casa en 2016</t>
+          <t>Población según si es capaz de moverse por su casa en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8807</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2486</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11496</t>
+          <t>12620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1569</t>
+          <t>1564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9324</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13755</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19147</t>
+          <t>19313</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5339</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>844</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>120534</t>
+          <t>119555</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131531</t>
+          <t>131626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154484</t>
+          <t>154915</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167867</t>
+          <t>168478</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>280199</t>
+          <t>280833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>297532</t>
+          <t>297879</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5507</t>
+          <t>6392</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>12357</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15550</t>
+          <t>14293</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23005</t>
+          <t>23285</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29560</t>
+          <t>31014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -7682,97 +7682,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1798</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5658</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>1187</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5941</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>5951</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1187</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>6459</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>151260</t>
+          <t>150984</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>161565</t>
+          <t>161445</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>187494</t>
+          <t>187672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>207781</t>
+          <t>207483</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>345076</t>
+          <t>343203</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>367103</t>
+          <t>366460</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8162</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>25073</t>
+          <t>25729</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -8251,97 +8251,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1918</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2297</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2122</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106616</t>
+          <t>106803</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114222</t>
+          <t>114136</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116813</t>
+          <t>116512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133860</t>
+          <t>134305</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227069</t>
+          <t>227984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246040</t>
+          <t>246677</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,75%</t>
         </is>
       </c>
     </row>
@@ -8594,97 +8594,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1754</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>8526</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>2467</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>8717</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>8355</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2467</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>7669</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>789</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5957</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21997</t>
+          <t>22189</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25230</t>
+          <t>27248</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -8825,7 +8825,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,62 +8855,62 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>1664</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>2341</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>5083</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>1664</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>5573</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162994</t>
+          <t>162111</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>173019</t>
+          <t>173048</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>218552</t>
+          <t>218158</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>236457</t>
+          <t>235286</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>386990</t>
+          <t>385604</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>405998</t>
+          <t>405666</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12312</t>
+          <t>10901</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22933</t>
+          <t>23840</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10430</t>
+          <t>10193</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29895</t>
+          <t>28742</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10471</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26146</t>
+          <t>26657</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32468</t>
+          <t>31484</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>61945</t>
+          <t>60317</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46248</t>
+          <t>47112</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78536</t>
+          <t>79493</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>841</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7905</t>
+          <t>8600</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>6952</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12256</t>
+          <t>12691</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9479,7 +9479,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>555556</t>
+          <t>554846</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>573135</t>
+          <t>573479</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>699363</t>
+          <t>700565</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>733543</t>
+          <t>734403</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1262261</t>
+          <t>1262250</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1300225</t>
+          <t>1300275</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de moverse por su casa en 2023</t>
+          <t>Población según si es capaz de moverse por su casa en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>351</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4479</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>927</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2101</t>
+          <t>2254</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6801</t>
+          <t>6949</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10097,7 +10097,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7974</t>
+          <t>8082</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16293</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20183</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>544</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>548</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5042</t>
+          <t>4850</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>139276</t>
+          <t>138797</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146078</t>
+          <t>146093</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>157693</t>
+          <t>157846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167217</t>
+          <t>167370</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>300338</t>
+          <t>299708</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>312351</t>
+          <t>311668</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>471</t>
+          <t>476</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5574</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2590</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8626</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>10840</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>21433</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13916</t>
+          <t>14361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26942</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>148396</t>
+          <t>147890</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156715</t>
+          <t>156366</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>189613</t>
+          <t>189925</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>202746</t>
+          <t>202374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>340391</t>
+          <t>340536</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>356689</t>
+          <t>356216</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>98</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11950</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>565</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9959</t>
+          <t>10490</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>860</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18051</t>
+          <t>16725</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17284</t>
+          <t>17060</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -11333,7 +11333,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4415</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>7157</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>419</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8412</t>
+          <t>8381</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128490</t>
+          <t>128875</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135635</t>
+          <t>135707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,82 +11456,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>99,09%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>347615</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>328163</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>357594</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>96,49%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>91,09%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>480972</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>466763</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>492436</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>93,88%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>99,04%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>347615</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>326041</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>357800</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>90,5%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,32%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>480972</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>466276</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>492947</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>93,78%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -11676,7 +11676,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4808</t>
+          <t>4728</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7267</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2401</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9522</t>
+          <t>9289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>463</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>17521</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9187</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20526</t>
+          <t>20926</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11902,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>4431</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7331</t>
+          <t>7459</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>196946</t>
+          <t>197028</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>203505</t>
+          <t>203192</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>250108</t>
+          <t>250142</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>262833</t>
+          <t>262566</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>450097</t>
+          <t>449690</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>464633</t>
+          <t>463915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2320</t>
+          <t>2365</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9648</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12260,42 +12260,42 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>15280</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>7598</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>22555</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
           <t>1,48%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>15280</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>7502</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>23116</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12578</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28454</t>
+          <t>29043</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18230</t>
+          <t>18045</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24273</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60436</t>
+          <t>60898</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>36329</t>
+          <t>34796</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70570</t>
+          <t>70411</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14975</t>
+          <t>15088</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6596</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18579</t>
+          <t>19022</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>623258</t>
+          <t>623232</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>637763</t>
+          <t>637518</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>942735</t>
+          <t>941764</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>996633</t>
+          <t>998187</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1576421</t>
+          <t>1577639</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1625900</t>
+          <t>1629348</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5416-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5416-Habitat-trans_orig.xlsx
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7868</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8240</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10945</t>
+          <t>11092</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>13761</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104044</t>
+          <t>103897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112366</t>
+          <t>113069</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>132939</t>
+          <t>132734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145412</t>
+          <t>145182</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>240973</t>
+          <t>241185</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>256422</t>
+          <t>256324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5300</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7747</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7494</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3229</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14699</t>
+          <t>15821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17408</t>
+          <t>17724</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4652</t>
+          <t>4399</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7182</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>856</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>8467</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135042</t>
+          <t>136676</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144855</t>
+          <t>144853</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>162828</t>
+          <t>162241</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>177017</t>
+          <t>176840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>303658</t>
+          <t>303937</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>319887</t>
+          <t>320152</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>891</t>
+          <t>890</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7819</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>877</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6804</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>11156</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>14545</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5603</t>
+          <t>5592</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>97763</t>
+          <t>97567</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120214</t>
+          <t>120233</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131748</t>
+          <t>131874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>221048</t>
+          <t>221363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>234623</t>
+          <t>234741</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,72%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5824</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>8493</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1689</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10239</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>809</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>928</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>929</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>9694</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130524</t>
+          <t>130580</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>136407</t>
+          <t>136419</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>193563</t>
+          <t>192170</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204704</t>
+          <t>205400</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>327115</t>
+          <t>327851</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>340244</t>
+          <t>340503</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>831</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>7807</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>4224</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>16618</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>21080</t>
+          <t>21256</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18310</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32747</t>
+          <t>32500</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>21365</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43671</t>
+          <t>43343</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>13626</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>480822</t>
+          <t>480006</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>494332</t>
+          <t>494104</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>625528</t>
+          <t>626168</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>649966</t>
+          <t>649874</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1112749</t>
+          <t>1113102</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1140217</t>
+          <t>1140342</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>9778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2186</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>7145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16129</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>19899</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>129601</t>
+          <t>129579</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>138475</t>
+          <t>138503</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>145303</t>
+          <t>144248</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>159242</t>
+          <t>158463</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>278723</t>
+          <t>278593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>295005</t>
+          <t>294804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11740</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16180</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21875</t>
+          <t>22851</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10946</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18943</t>
+          <t>18934</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24463</t>
+          <t>24512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5486</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>5788</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>8983</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>134610</t>
+          <t>136142</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>149286</t>
+          <t>149466</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>161701</t>
+          <t>159321</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>179028</t>
+          <t>178359</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>301886</t>
+          <t>302175</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>323608</t>
+          <t>324036</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,57%</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2981</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>15824</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17363</t>
+          <t>17654</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11888</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3150</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14525</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>10966</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>11442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>89764</t>
+          <t>89528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101580</t>
+          <t>102473</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116664</t>
+          <t>117689</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133341</t>
+          <t>133421</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213072</t>
+          <t>213643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>232583</t>
+          <t>232617</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12644</t>
+          <t>12660</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>2978</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14208</t>
+          <t>14053</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>8141</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16473</t>
+          <t>17243</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19900</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5783,7 +5783,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>7528</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>989</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8453</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149949</t>
+          <t>151157</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>159708</t>
+          <t>159700</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>215995</t>
+          <t>217695</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>233165</t>
+          <t>232506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>372907</t>
+          <t>372065</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>391043</t>
+          <t>390783</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4246</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18219</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38533</t>
+          <t>39001</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>26417</t>
+          <t>26025</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50890</t>
+          <t>50740</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6246</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19239</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24640</t>
+          <t>25773</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49031</t>
+          <t>49933</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34310</t>
+          <t>35247</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62494</t>
+          <t>62008</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13003</t>
+          <t>12403</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1142</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10961</t>
+          <t>11144</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>18815</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>523398</t>
+          <t>521963</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>543478</t>
+          <t>543602</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>658809</t>
+          <t>658248</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>690999</t>
+          <t>691399</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1189535</t>
+          <t>1191203</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1227225</t>
+          <t>1227944</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8972</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12620</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9324</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13903</t>
+          <t>13986</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19313</t>
+          <t>18479</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>5759</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5339</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7168,7 +7168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>848</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7335</t>
+          <t>8478</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7203,7 +7203,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>119555</t>
+          <t>120988</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>131626</t>
+          <t>131700</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>154915</t>
+          <t>154609</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>168478</t>
+          <t>168672</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>280833</t>
+          <t>280091</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>297879</t>
+          <t>297781</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6392</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7476,7 +7476,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12357</t>
+          <t>13499</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14293</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12714</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7553</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11875</t>
+          <t>11774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31014</t>
+          <t>30863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>150984</t>
+          <t>150262</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>161445</t>
+          <t>161457</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>187672</t>
+          <t>188284</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>207483</t>
+          <t>207601</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>343203</t>
+          <t>345013</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>366460</t>
+          <t>366231</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,35%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11025</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>882</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20945</t>
+          <t>21133</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8162</t>
+          <t>8899</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>25729</t>
+          <t>25781</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106803</t>
+          <t>106397</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114136</t>
+          <t>114153</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>116512</t>
+          <t>117543</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134305</t>
+          <t>134212</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227984</t>
+          <t>226880</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246677</t>
+          <t>245715</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8526</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>789</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10629</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22189</t>
+          <t>20639</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8737</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27248</t>
+          <t>25465</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -8825,7 +8825,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8895,7 +8895,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>162111</t>
+          <t>162356</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>173048</t>
+          <t>172582</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>218158</t>
+          <t>218758</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>235286</t>
+          <t>235213</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>385604</t>
+          <t>387096</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>405666</t>
+          <t>405556</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2434</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10901</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6324</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28742</t>
+          <t>28139</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>10594</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26657</t>
+          <t>26297</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31484</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60317</t>
+          <t>61120</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47112</t>
+          <t>47758</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79493</t>
+          <t>80679</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8659</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6952</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12691</t>
+          <t>12418</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>554846</t>
+          <t>554171</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>573479</t>
+          <t>573445</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>700565</t>
+          <t>699178</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>734403</t>
+          <t>734111</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1262250</t>
+          <t>1263226</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1300275</t>
+          <t>1300276</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>661</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>978</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>513</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16336</t>
+          <t>16685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>15081</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>10332</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>21294</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>544</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4918</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4850</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>143627</t>
+          <t>158272</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>138797</t>
+          <t>152953</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>146093</t>
+          <t>161320</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>163084</t>
+          <t>174019</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>157846</t>
+          <t>168196</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167370</t>
+          <t>178942</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>306711</t>
+          <t>332291</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>299708</t>
+          <t>325513</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>311668</t>
+          <t>338367</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,67 +10528,67 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>5393</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>5560</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>9820</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>1,21%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>5097</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2544</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>8666</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11381</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9263</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>15301</t>
+          <t>16606</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>24060</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>19704</t>
+          <t>21387</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14361</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27544</t>
+          <t>29360</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>598</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -10764,12 +10764,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1411</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -10799,12 +10799,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,22 +10824,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6466</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>153160</t>
+          <t>170822</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>147890</t>
+          <t>165382</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>156366</t>
+          <t>174255</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>196758</t>
+          <t>218463</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>189925</t>
+          <t>210187</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>202374</t>
+          <t>224391</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>349918</t>
+          <t>389284</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>340536</t>
+          <t>380064</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>356216</t>
+          <t>396690</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12164</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4130</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>565</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10490</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2548</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>6812</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6362</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16725</t>
+          <t>11053</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>8451</t>
+          <t>8910</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17060</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -11323,7 +11323,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1566</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -11333,12 +11333,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4260</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2391</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>8745</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>133357</t>
+          <t>155672</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>128875</t>
+          <t>150607</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>135707</t>
+          <t>158233</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>347615</t>
+          <t>161468</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>328163</t>
+          <t>154735</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>357594</t>
+          <t>166328</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>480972</t>
+          <t>317139</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>466763</t>
+          <t>309432</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>492436</t>
+          <t>323280</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1345</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -11676,12 +11676,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>3940</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7548</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>4941</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>9096</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -11779,22 +11779,22 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>492</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17521</t>
+          <t>21693</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>15865</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20926</t>
+          <t>24311</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -11902,12 +11902,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4431</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -11917,7 +11917,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>4207</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>201154</t>
+          <t>210751</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>197028</t>
+          <t>206744</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>203192</t>
+          <t>213183</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>257109</t>
+          <t>273266</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>250142</t>
+          <t>264897</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>262566</t>
+          <t>279842</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>458265</t>
+          <t>484016</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>449690</t>
+          <t>474352</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>463915</t>
+          <t>491254</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,24%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>275623</t>
+          <t>295366</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>480653</t>
+          <t>510454</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9585</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>16297</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7598</t>
+          <t>11367</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22555</t>
+          <t>23101</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29043</t>
+          <t>29103</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18045</t>
+          <t>19262</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>44809</t>
+          <t>49139</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23194</t>
+          <t>39861</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>60898</t>
+          <t>61319</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>55935</t>
+          <t>61243</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34796</t>
+          <t>50017</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70411</t>
+          <t>75451</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>7796</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>10692</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>9394</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19022</t>
+          <t>20799</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>631298</t>
+          <t>695516</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>623232</t>
+          <t>686842</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>637518</t>
+          <t>701867</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>964567</t>
+          <t>827214</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>941764</t>
+          <t>814699</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>998187</t>
+          <t>839662</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1595866</t>
+          <t>1522732</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1577639</t>
+          <t>1505590</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1629348</t>
+          <t>1536690</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
